--- a/player_performances.xlsx
+++ b/player_performances.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S113"/>
+  <dimension ref="A1:T113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,6 +524,11 @@
           <t>runouts</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -595,6 +600,9 @@
       <c r="S2" t="n">
         <v>0</v>
       </c>
+      <c r="T2" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -666,6 +674,9 @@
       <c r="S3" t="n">
         <v>0</v>
       </c>
+      <c r="T3" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -737,6 +748,9 @@
       <c r="S4" t="n">
         <v>0</v>
       </c>
+      <c r="T4" t="n">
+        <v>93</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -808,6 +822,9 @@
       <c r="S5" t="n">
         <v>0</v>
       </c>
+      <c r="T5" t="n">
+        <v>132</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -879,6 +896,9 @@
       <c r="S6" t="n">
         <v>0</v>
       </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -950,6 +970,9 @@
       <c r="S7" t="n">
         <v>0</v>
       </c>
+      <c r="T7" t="n">
+        <v>264</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1021,6 +1044,9 @@
       <c r="S8" t="n">
         <v>0</v>
       </c>
+      <c r="T8" t="n">
+        <v>195</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1092,6 +1118,9 @@
       <c r="S9" t="n">
         <v>0</v>
       </c>
+      <c r="T9" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1163,6 +1192,9 @@
       <c r="S10" t="n">
         <v>0</v>
       </c>
+      <c r="T10" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1234,6 +1266,9 @@
       <c r="S11" t="n">
         <v>0</v>
       </c>
+      <c r="T11" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1305,6 +1340,9 @@
       <c r="S12" t="n">
         <v>0</v>
       </c>
+      <c r="T12" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1376,6 +1414,9 @@
       <c r="S13" t="n">
         <v>0</v>
       </c>
+      <c r="T13" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1447,6 +1488,9 @@
       <c r="S14" t="n">
         <v>0</v>
       </c>
+      <c r="T14" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1518,6 +1562,9 @@
       <c r="S15" t="n">
         <v>0</v>
       </c>
+      <c r="T15" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1589,6 +1636,9 @@
       <c r="S16" t="n">
         <v>0</v>
       </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1660,6 +1710,9 @@
       <c r="S17" t="n">
         <v>1</v>
       </c>
+      <c r="T17" t="n">
+        <v>144</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1731,6 +1784,9 @@
       <c r="S18" t="n">
         <v>0</v>
       </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1802,6 +1858,9 @@
       <c r="S19" t="n">
         <v>0</v>
       </c>
+      <c r="T19" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1873,6 +1932,9 @@
       <c r="S20" t="n">
         <v>0</v>
       </c>
+      <c r="T20" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1944,6 +2006,9 @@
       <c r="S21" t="n">
         <v>1</v>
       </c>
+      <c r="T21" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2015,6 +2080,9 @@
       <c r="S22" t="n">
         <v>0</v>
       </c>
+      <c r="T22" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2086,6 +2154,9 @@
       <c r="S23" t="n">
         <v>0</v>
       </c>
+      <c r="T23" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2157,6 +2228,9 @@
       <c r="S24" t="n">
         <v>1</v>
       </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2228,6 +2302,9 @@
       <c r="S25" t="n">
         <v>0</v>
       </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2299,6 +2376,9 @@
       <c r="S26" t="n">
         <v>0</v>
       </c>
+      <c r="T26" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2370,6 +2450,9 @@
       <c r="S27" t="n">
         <v>0</v>
       </c>
+      <c r="T27" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2441,6 +2524,9 @@
       <c r="S28" t="n">
         <v>0</v>
       </c>
+      <c r="T28" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2512,6 +2598,9 @@
       <c r="S29" t="n">
         <v>0</v>
       </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2583,6 +2672,9 @@
       <c r="S30" t="n">
         <v>0</v>
       </c>
+      <c r="T30" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2654,6 +2746,9 @@
       <c r="S31" t="n">
         <v>0</v>
       </c>
+      <c r="T31" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2725,6 +2820,9 @@
       <c r="S32" t="n">
         <v>0</v>
       </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2796,6 +2894,9 @@
       <c r="S33" t="n">
         <v>0</v>
       </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2867,6 +2968,9 @@
       <c r="S34" t="n">
         <v>0</v>
       </c>
+      <c r="T34" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2938,6 +3042,9 @@
       <c r="S35" t="n">
         <v>0</v>
       </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3009,6 +3116,9 @@
       <c r="S36" t="n">
         <v>0</v>
       </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3080,6 +3190,9 @@
       <c r="S37" t="n">
         <v>1</v>
       </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3151,6 +3264,9 @@
       <c r="S38" t="n">
         <v>0</v>
       </c>
+      <c r="T38" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3222,6 +3338,9 @@
       <c r="S39" t="n">
         <v>0</v>
       </c>
+      <c r="T39" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3293,6 +3412,9 @@
       <c r="S40" t="n">
         <v>0</v>
       </c>
+      <c r="T40" t="n">
+        <v>36</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3364,6 +3486,9 @@
       <c r="S41" t="n">
         <v>1</v>
       </c>
+      <c r="T41" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3435,6 +3560,9 @@
       <c r="S42" t="n">
         <v>1</v>
       </c>
+      <c r="T42" t="n">
+        <v>74</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3506,6 +3634,9 @@
       <c r="S43" t="n">
         <v>0</v>
       </c>
+      <c r="T43" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3577,6 +3708,9 @@
       <c r="S44" t="n">
         <v>0</v>
       </c>
+      <c r="T44" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3648,6 +3782,9 @@
       <c r="S45" t="n">
         <v>3</v>
       </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3719,6 +3856,9 @@
       <c r="S46" t="n">
         <v>0</v>
       </c>
+      <c r="T46" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3790,6 +3930,9 @@
       <c r="S47" t="n">
         <v>0</v>
       </c>
+      <c r="T47" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3861,6 +4004,9 @@
       <c r="S48" t="n">
         <v>0</v>
       </c>
+      <c r="T48" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3932,6 +4078,9 @@
       <c r="S49" t="n">
         <v>0</v>
       </c>
+      <c r="T49" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4003,6 +4152,9 @@
       <c r="S50" t="n">
         <v>0</v>
       </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4074,6 +4226,9 @@
       <c r="S51" t="n">
         <v>0</v>
       </c>
+      <c r="T51" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4145,6 +4300,9 @@
       <c r="S52" t="n">
         <v>0</v>
       </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4216,6 +4374,9 @@
       <c r="S53" t="n">
         <v>0</v>
       </c>
+      <c r="T53" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4287,6 +4448,9 @@
       <c r="S54" t="n">
         <v>0</v>
       </c>
+      <c r="T54" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4358,6 +4522,9 @@
       <c r="S55" t="n">
         <v>0</v>
       </c>
+      <c r="T55" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4429,6 +4596,9 @@
       <c r="S56" t="n">
         <v>0</v>
       </c>
+      <c r="T56" t="n">
+        <v>122</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4500,6 +4670,9 @@
       <c r="S57" t="n">
         <v>0</v>
       </c>
+      <c r="T57" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4571,6 +4744,9 @@
       <c r="S58" t="n">
         <v>1</v>
       </c>
+      <c r="T58" t="n">
+        <v>76</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4642,6 +4818,9 @@
       <c r="S59" t="n">
         <v>0</v>
       </c>
+      <c r="T59" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4713,6 +4892,9 @@
       <c r="S60" t="n">
         <v>0</v>
       </c>
+      <c r="T60" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4784,6 +4966,9 @@
       <c r="S61" t="n">
         <v>0</v>
       </c>
+      <c r="T61" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4855,6 +5040,9 @@
       <c r="S62" t="n">
         <v>0</v>
       </c>
+      <c r="T62" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4926,6 +5114,9 @@
       <c r="S63" t="n">
         <v>0</v>
       </c>
+      <c r="T63" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4997,6 +5188,9 @@
       <c r="S64" t="n">
         <v>1</v>
       </c>
+      <c r="T64" t="n">
+        <v>94</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5068,6 +5262,9 @@
       <c r="S65" t="n">
         <v>0</v>
       </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5139,6 +5336,9 @@
       <c r="S66" t="n">
         <v>0</v>
       </c>
+      <c r="T66" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5210,6 +5410,9 @@
       <c r="S67" t="n">
         <v>0</v>
       </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5281,6 +5484,9 @@
       <c r="S68" t="n">
         <v>0</v>
       </c>
+      <c r="T68" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5352,6 +5558,9 @@
       <c r="S69" t="n">
         <v>1</v>
       </c>
+      <c r="T69" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5423,6 +5632,9 @@
       <c r="S70" t="n">
         <v>0</v>
       </c>
+      <c r="T70" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5494,6 +5706,9 @@
       <c r="S71" t="n">
         <v>1</v>
       </c>
+      <c r="T71" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5565,6 +5780,9 @@
       <c r="S72" t="n">
         <v>0</v>
       </c>
+      <c r="T72" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5636,6 +5854,9 @@
       <c r="S73" t="n">
         <v>0</v>
       </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5707,6 +5928,9 @@
       <c r="S74" t="n">
         <v>0</v>
       </c>
+      <c r="T74" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5778,6 +6002,9 @@
       <c r="S75" t="n">
         <v>0</v>
       </c>
+      <c r="T75" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5849,6 +6076,9 @@
       <c r="S76" t="n">
         <v>0</v>
       </c>
+      <c r="T76" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5920,6 +6150,9 @@
       <c r="S77" t="n">
         <v>0</v>
       </c>
+      <c r="T77" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5991,6 +6224,9 @@
       <c r="S78" t="n">
         <v>0</v>
       </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6062,6 +6298,9 @@
       <c r="S79" t="n">
         <v>0</v>
       </c>
+      <c r="T79" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6133,6 +6372,9 @@
       <c r="S80" t="n">
         <v>0</v>
       </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6204,6 +6446,9 @@
       <c r="S81" t="n">
         <v>0</v>
       </c>
+      <c r="T81" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6275,6 +6520,9 @@
       <c r="S82" t="n">
         <v>0</v>
       </c>
+      <c r="T82" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6346,6 +6594,9 @@
       <c r="S83" t="n">
         <v>0</v>
       </c>
+      <c r="T83" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6417,6 +6668,9 @@
       <c r="S84" t="n">
         <v>0</v>
       </c>
+      <c r="T84" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6488,6 +6742,9 @@
       <c r="S85" t="n">
         <v>1</v>
       </c>
+      <c r="T85" t="n">
+        <v>136</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6559,6 +6816,9 @@
       <c r="S86" t="n">
         <v>0</v>
       </c>
+      <c r="T86" t="n">
+        <v>144</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6630,6 +6890,9 @@
       <c r="S87" t="n">
         <v>0</v>
       </c>
+      <c r="T87" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6701,6 +6964,9 @@
       <c r="S88" t="n">
         <v>0</v>
       </c>
+      <c r="T88" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6772,6 +7038,9 @@
       <c r="S89" t="n">
         <v>0</v>
       </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6843,6 +7112,9 @@
       <c r="S90" t="n">
         <v>0</v>
       </c>
+      <c r="T90" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6914,6 +7186,9 @@
       <c r="S91" t="n">
         <v>0</v>
       </c>
+      <c r="T91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6985,6 +7260,9 @@
       <c r="S92" t="n">
         <v>1</v>
       </c>
+      <c r="T92" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7056,6 +7334,9 @@
       <c r="S93" t="n">
         <v>0</v>
       </c>
+      <c r="T93" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7127,6 +7408,9 @@
       <c r="S94" t="n">
         <v>0</v>
       </c>
+      <c r="T94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7198,6 +7482,9 @@
       <c r="S95" t="n">
         <v>0</v>
       </c>
+      <c r="T95" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7269,6 +7556,9 @@
       <c r="S96" t="n">
         <v>0</v>
       </c>
+      <c r="T96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7340,6 +7630,9 @@
       <c r="S97" t="n">
         <v>0</v>
       </c>
+      <c r="T97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7411,6 +7704,9 @@
       <c r="S98" t="n">
         <v>0</v>
       </c>
+      <c r="T98" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7482,6 +7778,9 @@
       <c r="S99" t="n">
         <v>0</v>
       </c>
+      <c r="T99" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7553,6 +7852,9 @@
       <c r="S100" t="n">
         <v>0</v>
       </c>
+      <c r="T100" t="n">
+        <v>192</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7624,6 +7926,9 @@
       <c r="S101" t="n">
         <v>0</v>
       </c>
+      <c r="T101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7695,6 +8000,9 @@
       <c r="S102" t="n">
         <v>0</v>
       </c>
+      <c r="T102" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7766,6 +8074,9 @@
       <c r="S103" t="n">
         <v>0</v>
       </c>
+      <c r="T103" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7837,6 +8148,9 @@
       <c r="S104" t="n">
         <v>0</v>
       </c>
+      <c r="T104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7908,6 +8222,9 @@
       <c r="S105" t="n">
         <v>0</v>
       </c>
+      <c r="T105" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7979,6 +8296,9 @@
       <c r="S106" t="n">
         <v>0</v>
       </c>
+      <c r="T106" t="n">
+        <v>140</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -8050,6 +8370,9 @@
       <c r="S107" t="n">
         <v>1</v>
       </c>
+      <c r="T107" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -8121,6 +8444,9 @@
       <c r="S108" t="n">
         <v>1</v>
       </c>
+      <c r="T108" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -8192,6 +8518,9 @@
       <c r="S109" t="n">
         <v>0</v>
       </c>
+      <c r="T109" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8263,6 +8592,9 @@
       <c r="S110" t="n">
         <v>0</v>
       </c>
+      <c r="T110" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -8334,6 +8666,9 @@
       <c r="S111" t="n">
         <v>0</v>
       </c>
+      <c r="T111" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -8405,6 +8740,9 @@
       <c r="S112" t="n">
         <v>0</v>
       </c>
+      <c r="T112" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -8475,6 +8813,9 @@
       </c>
       <c r="S113" t="n">
         <v>0</v>
+      </c>
+      <c r="T113" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/player_performances.xlsx
+++ b/player_performances.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T113"/>
+  <dimension ref="A1:S135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,11 +524,6 @@
           <t>runouts</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -539,9 +534,7 @@
       <c r="B2" t="n">
         <v>76411</v>
       </c>
-      <c r="C2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -600,9 +593,6 @@
       <c r="S2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="n">
-        <v>81</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -613,9 +603,7 @@
       <c r="B3" t="n">
         <v>76413</v>
       </c>
-      <c r="C3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -633,19 +621,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Malahide W1</t>
+          <t>Clontarf W1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>25 May 2026</t>
+          <t>30 May 2026</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -669,13 +657,10 @@
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -687,9 +672,7 @@
       <c r="B4" t="n">
         <v>76413</v>
       </c>
-      <c r="C4" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -707,22 +690,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>The Hills W1</t>
+          <t>Phoenix W1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>14 May 2026</t>
+          <t>30 May 2026</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -740,30 +723,25 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>93</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jenny Sparrow</t>
+          <t>Joanna Loughran</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74333</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1.1</v>
-      </c>
+        <v>76413</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -790,54 +768,49 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>1</v>
       </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>132</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jenny Sparrow</t>
+          <t>Joanna Loughran</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>74333</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1.1</v>
-      </c>
+        <v>76413</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -864,7 +837,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -873,30 +846,27 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>2</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>11</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -909,9 +879,7 @@
       <c r="B7" t="n">
         <v>74333</v>
       </c>
-      <c r="C7" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -924,42 +892,42 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pembroke W2</t>
+          <t>Clontarf W1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>12 May 2026</t>
+          <t>30 May 2026</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="J7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>31</v>
+      </c>
+      <c r="O7" t="n">
         <v>2</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>16</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3</v>
-      </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -969,23 +937,18 @@
       </c>
       <c r="S7" t="n">
         <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>264</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alex Sheedy</t>
+          <t>Jenny Sparrow</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3582562</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1.1</v>
-      </c>
+        <v>74333</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -1003,63 +966,58 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Malahide W1</t>
+          <t>Phoenix W1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>25 May 2026</t>
+          <t>30 May 2026</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="J8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
         <v>1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>195</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alex Sheedy</t>
+          <t>Jenny Sparrow</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3582562</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.1</v>
-      </c>
+        <v>74333</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -1077,37 +1035,37 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>The Hills W1</t>
+          <t>Malahide W1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>14 May 2026</t>
+          <t>25 May 2026</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1117,23 +1075,18 @@
       </c>
       <c r="S9" t="n">
         <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>150</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alex Sheedy</t>
+          <t>Jenny Sparrow</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3582562</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1.1</v>
-      </c>
+        <v>74333</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -1151,16 +1104,16 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Malahide W1</t>
+          <t>The Hills W1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>26 Apr 2026</t>
+          <t>14 May 2026</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1169,13 +1122,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1184,30 +1137,25 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rebecca Rolfe</t>
+          <t>Jenny Sparrow</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>91224</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1.2</v>
-      </c>
+        <v>74333</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -1220,42 +1168,42 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Leinster W1</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Malahide W1</t>
+          <t>Pembroke W2</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>25 May 2026</t>
+          <t>12 May 2026</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="J11" t="n">
+        <v>11</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>16</v>
+      </c>
+      <c r="O11" t="n">
         <v>3</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1265,23 +1213,18 @@
       </c>
       <c r="S11" t="n">
         <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rebecca Rolfe</t>
+          <t>Alex Sheedy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>91224</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1.2</v>
-      </c>
+        <v>3582562</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -1299,31 +1242,31 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>The Hills W1</t>
+          <t>Clontarf W1</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>14 May 2026</t>
+          <t>30 May 2026</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1339,23 +1282,18 @@
       </c>
       <c r="S12" t="n">
         <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>120</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Rebecca Rolfe</t>
+          <t>Alex Sheedy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>91224</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1.2</v>
-      </c>
+        <v>3582562</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -1373,37 +1311,37 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Malahide W1</t>
+          <t>Phoenix W1</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>26 Apr 2026</t>
+          <t>30 May 2026</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1413,23 +1351,18 @@
       </c>
       <c r="S13" t="n">
         <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Katie Dillon</t>
+          <t>Alex Sheedy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>104625</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1.2</v>
-      </c>
+        <v>3582562</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -1442,43 +1375,43 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Merrion W2</t>
+          <t>Malahide W1</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>26 May 2026</t>
+          <t>25 May 2026</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="J14" t="n">
+        <v>8</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>25</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
@@ -1487,23 +1420,18 @@
       </c>
       <c r="S14" t="n">
         <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Isabel Saeed-Maguire</t>
+          <t>Alex Sheedy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>74331</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1.2</v>
-      </c>
+        <v>3582562</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -1516,42 +1444,42 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Merrion W2</t>
+          <t>The Hills W1</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>26 May 2026</t>
+          <t>14 May 2026</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1561,23 +1489,18 @@
       </c>
       <c r="S15" t="n">
         <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Isabel Saeed-Maguire</t>
+          <t>Alex Sheedy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>74331</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1.2</v>
-      </c>
+        <v>3582562</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -1600,11 +1523,11 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>25 May 2026</t>
+          <t>26 Apr 2026</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1628,30 +1551,25 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Orla Bagnall</t>
+          <t>Rebecca Rolfe</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>110556</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1.2</v>
-      </c>
+        <v>91224</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -1664,42 +1582,42 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Merrion W2</t>
+          <t>Clontarf W1</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>26 May 2026</t>
+          <t>30 May 2026</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1708,24 +1626,19 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Orla Bagnall</t>
+          <t>Rebecca Rolfe</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>110556</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1.2</v>
-      </c>
+        <v>91224</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -1743,16 +1656,16 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Malahide W1</t>
+          <t>Phoenix W1</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>25 May 2026</t>
+          <t>30 May 2026</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1761,13 +1674,13 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -1782,24 +1695,19 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Orla Bagnall</t>
+          <t>Rebecca Rolfe</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>110556</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1.2</v>
-      </c>
+        <v>91224</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -1817,34 +1725,34 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>The Hills W1</t>
+          <t>Malahide W1</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>14 May 2026</t>
+          <t>25 May 2026</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -1857,23 +1765,18 @@
       </c>
       <c r="S19" t="n">
         <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Orla Bagnall</t>
+          <t>Rebecca Rolfe</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>110556</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1.2</v>
-      </c>
+        <v>91224</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -1886,36 +1789,36 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pembroke W2</t>
+          <t>The Hills W1</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>12 May 2026</t>
+          <t>14 May 2026</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -1931,23 +1834,18 @@
       </c>
       <c r="S20" t="n">
         <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Orla Bagnall</t>
+          <t>Rebecca Rolfe</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>110556</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1.2</v>
-      </c>
+        <v>91224</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -1974,7 +1872,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1983,16 +1881,16 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2004,66 +1902,61 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tash Richardson</t>
+          <t>Katie Dillon</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3389399</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1.2</v>
-      </c>
+        <v>104625</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
+          <t>Leinster W1</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Leinster W2</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>May2026</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Leinster W1</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Malahide W1</t>
+          <t>Merrion W2</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>26 Apr 2026</t>
+          <t>26 May 2026</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2079,26 +1972,21 @@
       </c>
       <c r="S22" t="n">
         <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Amy Kenealy</t>
+          <t>Isabel Saeed-Maguire</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>74266</v>
-      </c>
-      <c r="C23" t="n">
-        <v>2.1</v>
-      </c>
+        <v>74331</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2108,43 +1996,43 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pembroke W2</t>
+          <t>Clontarf W1</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>12 May 2026</t>
+          <t>30 May 2026</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
         <v>1</v>
       </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
@@ -2153,23 +2041,18 @@
       </c>
       <c r="S23" t="n">
         <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Isabella Merriman</t>
+          <t>Isabel Saeed-Maguire</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>327350</v>
-      </c>
-      <c r="C24" t="n">
-        <v>2.1</v>
-      </c>
+        <v>74331</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -2182,21 +2065,21 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Merrion W2</t>
+          <t>Phoenix W1</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>26 May 2026</t>
+          <t>30 May 2026</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2205,13 +2088,13 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -2226,24 +2109,19 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Isabella Merriman</t>
+          <t>Isabel Saeed-Maguire</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>327350</v>
-      </c>
-      <c r="C25" t="n">
-        <v>2.1</v>
-      </c>
+        <v>74331</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -2256,21 +2134,21 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Leinster W1</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Malahide W1</t>
+          <t>Merrion W2</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>25 May 2026</t>
+          <t>26 May 2026</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2300,24 +2178,19 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Isabella Merriman</t>
+          <t>Isabel Saeed-Maguire</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>327350</v>
-      </c>
-      <c r="C26" t="n">
-        <v>2.1</v>
-      </c>
+        <v>74331</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -2335,12 +2208,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>The Hills W1</t>
+          <t>Malahide W1</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>14 May 2026</t>
+          <t>25 May 2026</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -2353,16 +2226,16 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2375,23 +2248,18 @@
       </c>
       <c r="S26" t="n">
         <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Isabella Merriman</t>
+          <t>Orla Bagnall</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>327350</v>
-      </c>
-      <c r="C27" t="n">
-        <v>2.1</v>
-      </c>
+        <v>110556</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -2409,16 +2277,16 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Malahide W1</t>
+          <t>Clontarf W1</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>26 Apr 2026</t>
+          <t>30 May 2026</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2427,16 +2295,16 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2449,26 +2317,21 @@
       </c>
       <c r="S27" t="n">
         <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sue O'Connor</t>
+          <t>Orla Bagnall</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>74263</v>
-      </c>
-      <c r="C28" t="n">
-        <v>2.1</v>
-      </c>
+        <v>110556</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2478,39 +2341,39 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Merrion W2</t>
+          <t>Phoenix W1</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>26 May 2026</t>
+          <t>30 May 2026</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -2523,53 +2386,48 @@
       </c>
       <c r="S28" t="n">
         <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sue O'Connor</t>
+          <t>Orla Bagnall</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>74263</v>
-      </c>
-      <c r="C29" t="n">
-        <v>2.1</v>
-      </c>
+        <v>110556</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
+          <t>Leinster W1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>Leinster W2</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>May2026</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Leinster W1</t>
-        </is>
-      </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Malahide W1</t>
+          <t>Merrion W2</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>25 May 2026</t>
+          <t>26 May 2026</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2581,7 +2439,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -2596,27 +2454,22 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sue O'Connor</t>
+          <t>Orla Bagnall</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>74263</v>
-      </c>
-      <c r="C30" t="n">
-        <v>2.1</v>
-      </c>
+        <v>110556</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2626,17 +2479,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pembroke W2</t>
+          <t>Malahide W1</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>12 May 2026</t>
+          <t>25 May 2026</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -2649,16 +2502,16 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -2671,23 +2524,18 @@
       </c>
       <c r="S30" t="n">
         <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ella McMahon</t>
+          <t>Orla Bagnall</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>671119</v>
-      </c>
-      <c r="C31" t="n">
-        <v>2.1</v>
-      </c>
+        <v>110556</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -2700,42 +2548,42 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Merrion W2</t>
+          <t>The Hills W1</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>26 May 2026</t>
+          <t>14 May 2026</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2745,23 +2593,18 @@
       </c>
       <c r="S31" t="n">
         <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ella McMahon</t>
+          <t>Orla Bagnall</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>671119</v>
-      </c>
-      <c r="C32" t="n">
-        <v>2.1</v>
-      </c>
+        <v>110556</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -2774,36 +2617,36 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Leinster W1</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Malahide W1</t>
+          <t>Pembroke W2</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>25 May 2026</t>
+          <t>12 May 2026</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -2818,24 +2661,19 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ella McMahon</t>
+          <t>Orla Bagnall</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>671119</v>
-      </c>
-      <c r="C33" t="n">
-        <v>2.1</v>
-      </c>
+        <v>110556</v>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -2853,16 +2691,16 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>The Hills W1</t>
+          <t>Malahide W1</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>14 May 2026</t>
+          <t>26 Apr 2026</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2871,16 +2709,16 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -2892,27 +2730,22 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ella McMahon</t>
+          <t>Tash Richardson</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>671119</v>
-      </c>
-      <c r="C34" t="n">
-        <v>2.1</v>
-      </c>
+        <v>3389399</v>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Leinster W1</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2922,36 +2755,36 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pembroke W2</t>
+          <t>Malahide W1</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>12 May 2026</t>
+          <t>26 Apr 2026</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -2967,26 +2800,21 @@
       </c>
       <c r="S34" t="n">
         <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ella McMahon</t>
+          <t>Amy Kenealy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>671119</v>
-      </c>
-      <c r="C35" t="n">
-        <v>2.1</v>
-      </c>
+        <v>74266</v>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Leinster W1</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2996,40 +2824,40 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Leinster W1</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Malahide W1</t>
+          <t>Pembroke W2</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>26 Apr 2026</t>
+          <t>12 May 2026</t>
         </is>
       </c>
       <c r="I35" t="n">
+        <v>16</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>8</v>
+      </c>
+      <c r="O35" t="n">
         <v>1</v>
       </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
@@ -3041,26 +2869,21 @@
       </c>
       <c r="S35" t="n">
         <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Valmai Gee</t>
+          <t>Isabella Merriman</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>74309</v>
-      </c>
-      <c r="C36" t="n">
-        <v>2.2</v>
-      </c>
+        <v>327350</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3070,17 +2893,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rush W2</t>
+          <t>Clontarf W1</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>27 May 2026</t>
+          <t>30 May 2026</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -3093,13 +2916,13 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -3114,27 +2937,22 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Valmai Gee</t>
+          <t>Isabella Merriman</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>74309</v>
-      </c>
-      <c r="C37" t="n">
-        <v>2.2</v>
-      </c>
+        <v>327350</v>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3144,21 +2962,21 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Merrion W2</t>
+          <t>Phoenix W1</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>26 May 2026</t>
+          <t>30 May 2026</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3167,13 +2985,13 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -3188,51 +3006,46 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
-      </c>
-      <c r="T37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Valmai Gee</t>
+          <t>Isabella Merriman</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>74309</v>
-      </c>
-      <c r="C38" t="n">
-        <v>2.2</v>
-      </c>
+        <v>327350</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
+          <t>Leinster W1</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>Leinster W2</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>May2026</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Leinster W3</t>
-        </is>
-      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Balbriggan W2</t>
+          <t>Merrion W2</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>13 May 2026</t>
+          <t>26 May 2026</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3241,13 +3054,13 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -3259,30 +3072,25 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
         <v>1</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>44</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Valmai Gee</t>
+          <t>Isabella Merriman</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>74309</v>
-      </c>
-      <c r="C39" t="n">
-        <v>2.2</v>
-      </c>
+        <v>327350</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3292,17 +3100,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Clontarf W3</t>
+          <t>Malahide W1</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>5 May 2026</t>
+          <t>25 May 2026</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -3333,30 +3141,25 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Olivia Pacitto</t>
+          <t>Isabella Merriman</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>548731</v>
-      </c>
-      <c r="C40" t="n">
-        <v>2.2</v>
-      </c>
+        <v>327350</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3366,21 +3169,21 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phoenix W2</t>
+          <t>The Hills W1</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>19 May 2026</t>
+          <t>14 May 2026</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3389,13 +3192,13 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="O40" t="n">
         <v>1</v>
@@ -3412,25 +3215,20 @@
       <c r="S40" t="n">
         <v>0</v>
       </c>
-      <c r="T40" t="n">
-        <v>36</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Olivia Pacitto</t>
+          <t>Isabella Merriman</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>548731</v>
-      </c>
-      <c r="C41" t="n">
-        <v>2.2</v>
-      </c>
+        <v>327350</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3440,21 +3238,21 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Balbriggan W2</t>
+          <t>Malahide W1</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>13 May 2026</t>
+          <t>26 Apr 2026</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3463,16 +3261,16 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -3484,27 +3282,22 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
-      </c>
-      <c r="T41" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Katie Dagostino</t>
+          <t>Sue O'Connor</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>534286</v>
-      </c>
-      <c r="C42" t="n">
-        <v>2.2</v>
-      </c>
+        <v>74263</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Leinster W1</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3514,39 +3307,39 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pembroke W3</t>
+          <t>Phoenix W1</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>30 May 2026</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="O42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
@@ -3560,25 +3353,20 @@
       <c r="S42" t="n">
         <v>1</v>
       </c>
-      <c r="T42" t="n">
-        <v>74</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Katie Dagostino</t>
+          <t>Sue O'Connor</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>534286</v>
-      </c>
-      <c r="C43" t="n">
-        <v>2.2</v>
-      </c>
+        <v>74263</v>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Leinster W1</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3588,17 +3376,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phoenix W2</t>
+          <t>Merrion W2</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>19 May 2026</t>
+          <t>26 May 2026</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -3617,7 +3405,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="O43" t="n">
         <v>1</v>
@@ -3626,33 +3414,28 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>28</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Katie Dagostino</t>
+          <t>Sue O'Connor</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>534286</v>
-      </c>
-      <c r="C44" t="n">
-        <v>2.2</v>
-      </c>
+        <v>74263</v>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Leinster W1</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3667,12 +3450,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>The Hills W1</t>
+          <t>Malahide W1</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>14 May 2026</t>
+          <t>25 May 2026</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -3685,16 +3468,16 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="O44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -3707,26 +3490,21 @@
       </c>
       <c r="S44" t="n">
         <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Katie Dagostino</t>
+          <t>Sue O'Connor</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>534286</v>
-      </c>
-      <c r="C45" t="n">
-        <v>2.2</v>
-      </c>
+        <v>74263</v>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Leinster W1</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3736,17 +3514,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Balbriggan W2</t>
+          <t>Pembroke W2</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>13 May 2026</t>
+          <t>12 May 2026</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -3765,10 +3543,10 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
@@ -3780,24 +3558,19 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>3</v>
-      </c>
-      <c r="T45" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Katie Dagostino</t>
+          <t>Ella McMahon</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>534286</v>
-      </c>
-      <c r="C46" t="n">
-        <v>2.2</v>
-      </c>
+        <v>671119</v>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -3810,43 +3583,43 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Clontarf W3</t>
+          <t>Merrion W2</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>5 May 2026</t>
+          <t>26 May 2026</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
         <v>1</v>
       </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
@@ -3855,23 +3628,18 @@
       </c>
       <c r="S46" t="n">
         <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Katie Dagostino</t>
+          <t>Ella McMahon</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>534286</v>
-      </c>
-      <c r="C47" t="n">
-        <v>2.2</v>
-      </c>
+        <v>671119</v>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -3894,11 +3662,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>26 Apr 2026</t>
+          <t>25 May 2026</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3907,16 +3675,16 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
@@ -3929,23 +3697,18 @@
       </c>
       <c r="S47" t="n">
         <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>28</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Nazli Leetch</t>
+          <t>Ella McMahon</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>882252</v>
-      </c>
-      <c r="C48" t="n">
-        <v>2.2</v>
-      </c>
+        <v>671119</v>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -3958,42 +3721,42 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rush W2</t>
+          <t>The Hills W1</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>27 May 2026</t>
+          <t>14 May 2026</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -4003,23 +3766,18 @@
       </c>
       <c r="S48" t="n">
         <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Nazli Leetch</t>
+          <t>Ella McMahon</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>882252</v>
-      </c>
-      <c r="C49" t="n">
-        <v>2.2</v>
-      </c>
+        <v>671119</v>
+      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -4032,24 +3790,24 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phoenix W2</t>
+          <t>Pembroke W2</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>19 May 2026</t>
+          <t>12 May 2026</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -4067,7 +3825,7 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -4077,23 +3835,18 @@
       </c>
       <c r="S49" t="n">
         <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Nazli Leetch</t>
+          <t>Ella McMahon</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>882252</v>
-      </c>
-      <c r="C50" t="n">
-        <v>2.2</v>
-      </c>
+        <v>671119</v>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -4106,21 +3859,21 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pembroke W2</t>
+          <t>Malahide W1</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>12 May 2026</t>
+          <t>26 Apr 2026</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4151,26 +3904,21 @@
       </c>
       <c r="S50" t="n">
         <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Nazli Leetch</t>
+          <t>Valmai Gee</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>882252</v>
-      </c>
-      <c r="C51" t="n">
-        <v>2.2</v>
-      </c>
+        <v>74309</v>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Leinster W1</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4180,17 +3928,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Leinster W1</t>
+          <t>Leinster W3</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Malahide W1</t>
+          <t>Rush W2</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>26 Apr 2026</t>
+          <t>27 May 2026</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -4203,19 +3951,19 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -4225,26 +3973,21 @@
       </c>
       <c r="S51" t="n">
         <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Leah Mullett</t>
+          <t>Valmai Gee</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>327209</v>
-      </c>
-      <c r="C52" t="n">
-        <v>3.1</v>
-      </c>
+        <v>74309</v>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4254,17 +3997,17 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Clontarf W3</t>
+          <t>Merrion W2</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>5 May 2026</t>
+          <t>26 May 2026</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -4298,27 +4041,22 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Lauren Torpey</t>
+          <t>Valmai Gee</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>661554</v>
-      </c>
-      <c r="C53" t="n">
-        <v>3.1</v>
-      </c>
+        <v>74309</v>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Leinster W1</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4333,34 +4071,34 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rush W2</t>
+          <t>Balbriggan W2</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>27 May 2026</t>
+          <t>13 May 2026</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="J53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
@@ -4369,30 +4107,25 @@
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>126</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Lauren Torpey</t>
+          <t>Valmai Gee</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>661554</v>
-      </c>
-      <c r="C54" t="n">
-        <v>3.1</v>
-      </c>
+        <v>74309</v>
+      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Leinster W1</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4402,21 +4135,21 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W3</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Merrion W2</t>
+          <t>Clontarf W3</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>26 May 2026</t>
+          <t>5 May 2026</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4425,13 +4158,13 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -4443,30 +4176,25 @@
         <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Lauren Torpey</t>
+          <t>Olivia Pacitto</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>661554</v>
-      </c>
-      <c r="C55" t="n">
-        <v>3.1</v>
-      </c>
+        <v>548731</v>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Leinster W1</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4476,21 +4204,21 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Leinster W1</t>
+          <t>Leinster W3</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Malahide W1</t>
+          <t>Phoenix W2</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>25 May 2026</t>
+          <t>19 May 2026</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4505,7 +4233,7 @@
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O55" t="n">
         <v>1</v>
@@ -4522,25 +4250,20 @@
       <c r="S55" t="n">
         <v>0</v>
       </c>
-      <c r="T55" t="n">
-        <v>8</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Lauren Torpey</t>
+          <t>Olivia Pacitto</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>661554</v>
-      </c>
-      <c r="C56" t="n">
-        <v>3.1</v>
-      </c>
+        <v>548731</v>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Leinster W1</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4555,16 +4278,16 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phoenix W2</t>
+          <t>Balbriggan W2</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>19 May 2026</t>
+          <t>13 May 2026</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -4573,13 +4296,13 @@
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -4588,30 +4311,25 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>122</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Lauren Torpey</t>
+          <t>Katie Dagostino</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>661554</v>
-      </c>
-      <c r="C57" t="n">
-        <v>3.1</v>
-      </c>
+        <v>534286</v>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -4624,68 +4342,63 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Leinster W1</t>
+          <t>Leinster W3</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>The Hills W1</t>
+          <t>Pembroke W3</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>14 May 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="O57" t="n">
         <v>1</v>
       </c>
       <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
         <v>1</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Lauren Torpey</t>
+          <t>Katie Dagostino</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>661554</v>
-      </c>
-      <c r="C58" t="n">
-        <v>3.1</v>
-      </c>
+        <v>534286</v>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -4703,16 +4416,16 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Balbriggan W2</t>
+          <t>Phoenix W2</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>13 May 2026</t>
+          <t>19 May 2026</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -4727,7 +4440,7 @@
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O58" t="n">
         <v>1</v>
@@ -4736,30 +4449,25 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
-      </c>
-      <c r="T58" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Lauren Torpey</t>
+          <t>Katie Dagostino</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>661554</v>
-      </c>
-      <c r="C59" t="n">
-        <v>3.1</v>
-      </c>
+        <v>534286</v>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -4772,17 +4480,17 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pembroke W2</t>
+          <t>The Hills W1</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>12 May 2026</t>
+          <t>14 May 2026</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -4795,19 +4503,19 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>5</v>
+      </c>
+      <c r="O59" t="n">
         <v>2</v>
       </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>12</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
       <c r="P59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -4817,23 +4525,18 @@
       </c>
       <c r="S59" t="n">
         <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Lauren Torpey</t>
+          <t>Katie Dagostino</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>661554</v>
-      </c>
-      <c r="C60" t="n">
-        <v>3.1</v>
-      </c>
+        <v>534286</v>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -4851,63 +4554,58 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Clontarf W3</t>
+          <t>Balbriggan W2</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>5 May 2026</t>
+          <t>13 May 2026</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
       <c r="L60" t="n">
+        <v>4</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>19</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
         <v>3</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>18</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>100</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ursula Oliver</t>
+          <t>Katie Dagostino</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>662721</v>
-      </c>
-      <c r="C61" t="n">
-        <v>3.1</v>
-      </c>
+        <v>534286</v>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -4925,19 +4623,19 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rush W2</t>
+          <t>Clontarf W3</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>27 May 2026</t>
+          <t>5 May 2026</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -4949,10 +4647,10 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
@@ -4965,23 +4663,18 @@
       </c>
       <c r="S61" t="n">
         <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>58</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Ursula Oliver</t>
+          <t>Katie Dagostino</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>662721</v>
-      </c>
-      <c r="C62" t="n">
-        <v>3.1</v>
-      </c>
+        <v>534286</v>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -4994,21 +4687,21 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Merrion W2</t>
+          <t>Malahide W1</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>26 May 2026</t>
+          <t>26 Apr 2026</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5017,16 +4710,16 @@
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="O62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
@@ -5039,23 +4732,18 @@
       </c>
       <c r="S62" t="n">
         <v>0</v>
-      </c>
-      <c r="T62" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ursula Oliver</t>
+          <t>Nazli Leetch</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>662721</v>
-      </c>
-      <c r="C63" t="n">
-        <v>3.1</v>
-      </c>
+        <v>882252</v>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -5073,37 +4761,37 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phoenix W2</t>
+          <t>Rush W2</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>19 May 2026</t>
+          <t>27 May 2026</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -5113,23 +4801,18 @@
       </c>
       <c r="S63" t="n">
         <v>0</v>
-      </c>
-      <c r="T63" t="n">
-        <v>44</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Ursula Oliver</t>
+          <t>Nazli Leetch</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>662721</v>
-      </c>
-      <c r="C64" t="n">
-        <v>3.1</v>
-      </c>
+        <v>882252</v>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -5147,16 +4830,16 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Balbriggan W2</t>
+          <t>Phoenix W2</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>13 May 2026</t>
+          <t>19 May 2026</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5165,19 +4848,19 @@
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -5186,24 +4869,19 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
-      </c>
-      <c r="T64" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ursula Oliver</t>
+          <t>Nazli Leetch</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>662721</v>
-      </c>
-      <c r="C65" t="n">
-        <v>3.1</v>
-      </c>
+        <v>882252</v>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -5230,7 +4908,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5260,24 +4938,19 @@
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Ursula Oliver</t>
+          <t>Nazli Leetch</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>662721</v>
-      </c>
-      <c r="C66" t="n">
-        <v>3.1</v>
-      </c>
+        <v>882252</v>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>Leinster W1</t>
@@ -5290,24 +4963,24 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Clontarf W3</t>
+          <t>Malahide W1</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>5 May 2026</t>
+          <t>26 Apr 2026</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -5319,13 +4992,13 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -5335,26 +5008,21 @@
       </c>
       <c r="S66" t="n">
         <v>0</v>
-      </c>
-      <c r="T66" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Ursula Oliver</t>
+          <t>Leah Mullett</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>662721</v>
-      </c>
-      <c r="C67" t="n">
-        <v>3.1</v>
-      </c>
+        <v>327209</v>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Leinster W1</t>
+          <t>Leinster W3</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5364,17 +5032,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Leinster W1</t>
+          <t>Leinster W3</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Malahide W1</t>
+          <t>Clontarf W3</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>26 Apr 2026</t>
+          <t>5 May 2026</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -5408,27 +5076,22 @@
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Aisling O'Kelly</t>
+          <t>Lauren Torpey</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>893163</v>
-      </c>
-      <c r="C68" t="n">
-        <v>3.1</v>
-      </c>
+        <v>661554</v>
+      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5438,21 +5101,21 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Rush W2</t>
+          <t>Clontarf W1</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>27 May 2026</t>
+          <t>30 May 2026</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5467,10 +5130,10 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="O68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P68" t="n">
         <v>0</v>
@@ -5483,26 +5146,21 @@
       </c>
       <c r="S68" t="n">
         <v>0</v>
-      </c>
-      <c r="T68" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Aisling O'Kelly</t>
+          <t>Lauren Torpey</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>893163</v>
-      </c>
-      <c r="C69" t="n">
-        <v>3.1</v>
-      </c>
+        <v>661554</v>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5512,21 +5170,21 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Merrion W2</t>
+          <t>Phoenix W1</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>26 May 2026</t>
+          <t>30 May 2026</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5535,19 +5193,19 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
@@ -5556,69 +5214,64 @@
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
-      </c>
-      <c r="T69" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Aisling O'Kelly</t>
+          <t>Lauren Torpey</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>893163</v>
-      </c>
-      <c r="C70" t="n">
-        <v>3.1</v>
-      </c>
+        <v>661554</v>
+      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
+          <t>Leinster W1</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t>Leinster W3</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>May2026</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Leinster W1</t>
-        </is>
-      </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Malahide W1</t>
+          <t>Rush W2</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>25 May 2026</t>
+          <t>27 May 2026</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="O70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P70" t="n">
         <v>0</v>
@@ -5631,26 +5284,21 @@
       </c>
       <c r="S70" t="n">
         <v>0</v>
-      </c>
-      <c r="T70" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Aisling O'Kelly</t>
+          <t>Lauren Torpey</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>893163</v>
-      </c>
-      <c r="C71" t="n">
-        <v>3.1</v>
-      </c>
+        <v>661554</v>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5660,21 +5308,21 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pembroke W3</t>
+          <t>Merrion W2</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>26 May 2026</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5683,16 +5331,16 @@
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="O71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
         <v>0</v>
@@ -5704,27 +5352,22 @@
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
-      </c>
-      <c r="T71" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Aisling O'Kelly</t>
+          <t>Lauren Torpey</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>893163</v>
-      </c>
-      <c r="C72" t="n">
-        <v>3.1</v>
-      </c>
+        <v>661554</v>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5739,12 +5382,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>The Hills W1</t>
+          <t>Malahide W1</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>14 May 2026</t>
+          <t>25 May 2026</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -5757,16 +5400,16 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="O72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P72" t="n">
         <v>0</v>
@@ -5779,50 +5422,45 @@
       </c>
       <c r="S72" t="n">
         <v>0</v>
-      </c>
-      <c r="T72" t="n">
-        <v>28</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Aisling O'Kelly</t>
+          <t>Lauren Torpey</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>893163</v>
-      </c>
-      <c r="C73" t="n">
-        <v>3.1</v>
-      </c>
+        <v>661554</v>
+      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
+          <t>Leinster W1</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t>Leinster W3</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>May2026</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Leinster W3</t>
-        </is>
-      </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Balbriggan W2</t>
+          <t>Phoenix W2</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>13 May 2026</t>
+          <t>19 May 2026</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -5831,13 +5469,13 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -5846,33 +5484,28 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
-      </c>
-      <c r="T73" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Aisling O'Kelly</t>
+          <t>Lauren Torpey</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>893163</v>
-      </c>
-      <c r="C74" t="n">
-        <v>3.1</v>
-      </c>
+        <v>661554</v>
+      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5882,42 +5515,42 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pembroke W2</t>
+          <t>The Hills W1</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>12 May 2026</t>
+          <t>14 May 2026</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q74" t="n">
         <v>0</v>
@@ -5927,50 +5560,45 @@
       </c>
       <c r="S74" t="n">
         <v>0</v>
-      </c>
-      <c r="T74" t="n">
-        <v>44</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Aisling O'Kelly</t>
+          <t>Lauren Torpey</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>893163</v>
-      </c>
-      <c r="C75" t="n">
-        <v>3.1</v>
-      </c>
+        <v>661554</v>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
+          <t>Leinster W1</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t>Leinster W3</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>May2026</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Leinster W3</t>
-        </is>
-      </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Clontarf W3</t>
+          <t>Balbriggan W2</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>5 May 2026</t>
+          <t>13 May 2026</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -5979,13 +5607,13 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O75" t="n">
         <v>1</v>
@@ -6000,27 +5628,22 @@
         <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>0</v>
-      </c>
-      <c r="T75" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Aisling O'Kelly</t>
+          <t>Lauren Torpey</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>893163</v>
-      </c>
-      <c r="C76" t="n">
-        <v>3.1</v>
-      </c>
+        <v>661554</v>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6030,21 +5653,21 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Leinster W1</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Malahide W1</t>
+          <t>Pembroke W2</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>26 Apr 2026</t>
+          <t>12 May 2026</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6053,16 +5676,16 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="O76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P76" t="n">
         <v>1</v>
@@ -6076,70 +5699,65 @@
       <c r="S76" t="n">
         <v>0</v>
       </c>
-      <c r="T76" t="n">
-        <v>28</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Isabella McGrath</t>
+          <t>Lauren Torpey</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>546310</v>
-      </c>
-      <c r="C77" t="n">
-        <v>3.1</v>
-      </c>
+        <v>661554</v>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
+          <t>Leinster W1</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t>Leinster W3</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>May2026</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Leinster W3</t>
-        </is>
-      </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pembroke W3</t>
+          <t>Clontarf W3</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>5 May 2026</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -6149,26 +5767,21 @@
       </c>
       <c r="S77" t="n">
         <v>0</v>
-      </c>
-      <c r="T77" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sinead O'Shea</t>
+          <t>Ursula Oliver</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>882428</v>
-      </c>
-      <c r="C78" t="n">
-        <v>3.2</v>
-      </c>
+        <v>662721</v>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -6178,17 +5791,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rush W2</t>
+          <t>Clontarf W1</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>27 May 2026</t>
+          <t>30 May 2026</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -6222,27 +5835,22 @@
         <v>0</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
-      </c>
-      <c r="T78" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Ava Deacon</t>
+          <t>Ursula Oliver</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>326899</v>
-      </c>
-      <c r="C79" t="n">
-        <v>3.2</v>
-      </c>
+        <v>662721</v>
+      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -6252,39 +5860,39 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rush W2</t>
+          <t>Phoenix W1</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>27 May 2026</t>
+          <t>30 May 2026</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P79" t="n">
         <v>0</v>
@@ -6297,65 +5905,60 @@
       </c>
       <c r="S79" t="n">
         <v>0</v>
-      </c>
-      <c r="T79" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Ava Deacon</t>
+          <t>Ursula Oliver</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>326899</v>
-      </c>
-      <c r="C80" t="n">
-        <v>3.2</v>
-      </c>
+        <v>662721</v>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
+          <t>Leinster W1</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t>Leinster W3</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>May2026</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Leinster W2</t>
-        </is>
-      </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Merrion W2</t>
+          <t>Rush W2</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>26 May 2026</t>
+          <t>27 May 2026</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -6370,27 +5973,22 @@
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
-      </c>
-      <c r="T80" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Ava Deacon</t>
+          <t>Ursula Oliver</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>326899</v>
-      </c>
-      <c r="C81" t="n">
-        <v>3.2</v>
-      </c>
+        <v>662721</v>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -6400,24 +5998,24 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pembroke W3</t>
+          <t>Merrion W2</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>26 May 2026</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -6429,7 +6027,7 @@
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="O81" t="n">
         <v>2</v>
@@ -6446,37 +6044,32 @@
       <c r="S81" t="n">
         <v>0</v>
       </c>
-      <c r="T81" t="n">
-        <v>32</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Ava Deacon</t>
+          <t>Ursula Oliver</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>326899</v>
-      </c>
-      <c r="C82" t="n">
-        <v>3.2</v>
-      </c>
+        <v>662721</v>
+      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
+          <t>Leinster W1</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>Leinster W3</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>May2026</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Leinster W3</t>
-        </is>
-      </c>
       <c r="G82" t="inlineStr">
         <is>
           <t>Phoenix W2</t>
@@ -6488,7 +6081,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6497,16 +6090,16 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P82" t="n">
         <v>0</v>
@@ -6519,50 +6112,45 @@
       </c>
       <c r="S82" t="n">
         <v>0</v>
-      </c>
-      <c r="T82" t="n">
-        <v>38</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Ava Deacon</t>
+          <t>Ursula Oliver</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>326899</v>
-      </c>
-      <c r="C83" t="n">
-        <v>3.2</v>
-      </c>
+        <v>662721</v>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
+          <t>Leinster W1</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t>Leinster W3</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>May2026</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Leinster W2</t>
-        </is>
-      </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pembroke W2</t>
+          <t>Balbriggan W2</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>12 May 2026</t>
+          <t>13 May 2026</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -6571,16 +6159,16 @@
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P83" t="n">
         <v>0</v>
@@ -6592,27 +6180,22 @@
         <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
-      </c>
-      <c r="T83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Ava Deacon</t>
+          <t>Ursula Oliver</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>326899</v>
-      </c>
-      <c r="C84" t="n">
-        <v>3.2</v>
-      </c>
+        <v>662721</v>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -6622,39 +6205,39 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Clontarf W3</t>
+          <t>Pembroke W2</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>5 May 2026</t>
+          <t>12 May 2026</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P84" t="n">
         <v>0</v>
@@ -6667,26 +6250,21 @@
       </c>
       <c r="S84" t="n">
         <v>0</v>
-      </c>
-      <c r="T84" t="n">
-        <v>38</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Daphne Deacon</t>
+          <t>Ursula Oliver</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>691434</v>
-      </c>
-      <c r="C85" t="n">
-        <v>4</v>
-      </c>
+        <v>662721</v>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Leinster W4</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -6696,21 +6274,21 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Leinster W4</t>
+          <t>Leinster W3</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Athlone W1</t>
+          <t>Clontarf W3</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>23 May 2026</t>
+          <t>5 May 2026</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J85" t="n">
         <v>4</v>
@@ -6719,19 +6297,19 @@
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -6740,27 +6318,22 @@
         <v>0</v>
       </c>
       <c r="S85" t="n">
-        <v>1</v>
-      </c>
-      <c r="T85" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Daphne Deacon</t>
+          <t>Ursula Oliver</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>691434</v>
-      </c>
-      <c r="C86" t="n">
-        <v>4</v>
-      </c>
+        <v>662721</v>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Leinster W4</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -6770,21 +6343,21 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Leinster W4</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tyrrelstown W1</t>
+          <t>Malahide W1</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>14 May 2026</t>
+          <t>26 Apr 2026</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -6793,13 +6366,13 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -6815,65 +6388,60 @@
       </c>
       <c r="S86" t="n">
         <v>0</v>
-      </c>
-      <c r="T86" t="n">
-        <v>144</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Margaret O'Donoghue</t>
+          <t>Aisling O'Kelly</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>554268</v>
-      </c>
-      <c r="C87" t="n">
+        <v>893163</v>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Leinster W1</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Clontarf W1</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>30 May 2026</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>5</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
         <v>4</v>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Leinster W3</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>May2026</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Leinster W4</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Athlone W1</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>23 May 2026</t>
-        </is>
-      </c>
-      <c r="I87" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" t="n">
-        <v>3</v>
-      </c>
       <c r="M87" t="n">
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="O87" t="n">
         <v>1</v>
@@ -6890,67 +6458,62 @@
       <c r="S87" t="n">
         <v>0</v>
       </c>
-      <c r="T87" t="n">
-        <v>16</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Margaret O'Donoghue</t>
+          <t>Aisling O'Kelly</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>554268</v>
-      </c>
-      <c r="C88" t="n">
+        <v>893163</v>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Leinster W1</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Phoenix W1</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>30 May 2026</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>15</v>
+      </c>
+      <c r="J88" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
         <v>4</v>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Leinster W3</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>May2026</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Leinster W4</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Tyrrelstown W1</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>14 May 2026</t>
-        </is>
-      </c>
-      <c r="I88" t="n">
-        <v>3</v>
-      </c>
-      <c r="J88" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" t="n">
-        <v>2</v>
-      </c>
       <c r="M88" t="n">
         <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P88" t="n">
         <v>0</v>
@@ -6963,51 +6526,46 @@
       </c>
       <c r="S88" t="n">
         <v>0</v>
-      </c>
-      <c r="T88" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Margaret O'Donoghue</t>
+          <t>Aisling O'Kelly</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>554268</v>
-      </c>
-      <c r="C89" t="n">
+        <v>893163</v>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Rush W2</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>27 May 2026</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
         <v>4</v>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Leinster W3</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>May2026</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Leinster W3</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Clontarf W3</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>5 May 2026</t>
-        </is>
-      </c>
-      <c r="I89" t="n">
-        <v>0</v>
-      </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
@@ -7015,16 +6573,16 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P89" t="n">
         <v>0</v>
@@ -7036,24 +6594,19 @@
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T89" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Alison Crawford</t>
+          <t>Aisling O'Kelly</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>76412</v>
-      </c>
-      <c r="C90" t="n">
-        <v>4</v>
-      </c>
+        <v>893163</v>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
           <t>Leinster W3</t>
@@ -7066,17 +6619,17 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Leinster W4</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tyrrelstown W1</t>
+          <t>Merrion W2</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>14 May 2026</t>
+          <t>26 May 2026</t>
         </is>
       </c>
       <c r="I90" t="n">
@@ -7089,19 +6642,19 @@
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -7110,69 +6663,64 @@
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sadhbh Smyth</t>
+          <t>Aisling O'Kelly</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3281758</v>
-      </c>
-      <c r="C91" t="n">
+        <v>893163</v>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Leinster W1</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Malahide W1</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>25 May 2026</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
         <v>4</v>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Leinster W3</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>May2026</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Leinster W3</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Rush W2</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>27 May 2026</t>
-        </is>
-      </c>
-      <c r="I91" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" t="n">
-        <v>3</v>
-      </c>
       <c r="M91" t="n">
         <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P91" t="n">
         <v>0</v>
@@ -7184,24 +6732,19 @@
         <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>0</v>
-      </c>
-      <c r="T91" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sadhbh Smyth</t>
+          <t>Aisling O'Kelly</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3281758</v>
-      </c>
-      <c r="C92" t="n">
-        <v>4</v>
-      </c>
+        <v>893163</v>
+      </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
           <t>Leinster W3</t>
@@ -7214,24 +6757,24 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Leinster W4</t>
+          <t>Leinster W3</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Athlone W1</t>
+          <t>Pembroke W3</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>23 May 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -7243,10 +6786,10 @@
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P92" t="n">
         <v>0</v>
@@ -7260,22 +6803,17 @@
       <c r="S92" t="n">
         <v>1</v>
       </c>
-      <c r="T92" t="n">
-        <v>56</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sadhbh Smyth</t>
+          <t>Aisling O'Kelly</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3281758</v>
-      </c>
-      <c r="C93" t="n">
-        <v>4</v>
-      </c>
+        <v>893163</v>
+      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
           <t>Leinster W3</t>
@@ -7288,17 +6826,17 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pembroke W3</t>
+          <t>The Hills W1</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>14 May 2026</t>
         </is>
       </c>
       <c r="I93" t="n">
@@ -7311,16 +6849,16 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P93" t="n">
         <v>0</v>
@@ -7333,65 +6871,60 @@
       </c>
       <c r="S93" t="n">
         <v>0</v>
-      </c>
-      <c r="T93" t="n">
-        <v>32</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sadhbh Smyth</t>
+          <t>Aisling O'Kelly</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>3281758</v>
-      </c>
-      <c r="C94" t="n">
+        <v>893163</v>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Balbriggan W2</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>13 May 2026</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
         <v>4</v>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Leinster W3</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>May2026</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Leinster W3</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Phoenix W2</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>19 May 2026</t>
-        </is>
-      </c>
-      <c r="I94" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" t="n">
-        <v>0</v>
-      </c>
       <c r="M94" t="n">
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -7406,24 +6939,19 @@
         <v>0</v>
       </c>
       <c r="S94" t="n">
-        <v>0</v>
-      </c>
-      <c r="T94" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sadhbh Smyth</t>
+          <t>Aisling O'Kelly</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>3281758</v>
-      </c>
-      <c r="C95" t="n">
-        <v>4</v>
-      </c>
+        <v>893163</v>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
           <t>Leinster W3</t>
@@ -7436,39 +6964,39 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Leinster W4</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tyrrelstown W1</t>
+          <t>Pembroke W2</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>14 May 2026</t>
+          <t>12 May 2026</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P95" t="n">
         <v>0</v>
@@ -7481,23 +7009,18 @@
       </c>
       <c r="S95" t="n">
         <v>0</v>
-      </c>
-      <c r="T95" t="n">
-        <v>48</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sadhbh Smyth</t>
+          <t>Aisling O'Kelly</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>3281758</v>
-      </c>
-      <c r="C96" t="n">
-        <v>4</v>
-      </c>
+        <v>893163</v>
+      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>Leinster W3</t>
@@ -7515,12 +7038,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Balbriggan W2</t>
+          <t>Clontarf W3</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>13 May 2026</t>
+          <t>5 May 2026</t>
         </is>
       </c>
       <c r="I96" t="n">
@@ -7533,16 +7056,16 @@
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P96" t="n">
         <v>0</v>
@@ -7554,72 +7077,67 @@
         <v>0</v>
       </c>
       <c r="S96" t="n">
-        <v>0</v>
-      </c>
-      <c r="T96" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sadhbh Smyth</t>
+          <t>Aisling O'Kelly</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>3281758</v>
-      </c>
-      <c r="C97" t="n">
+        <v>893163</v>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Leinster W1</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Malahide W1</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>26 Apr 2026</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>6</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
         <v>4</v>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Leinster W3</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>May2026</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Leinster W3</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Clontarf W3</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>5 May 2026</t>
-        </is>
-      </c>
-      <c r="I97" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" t="n">
-        <v>0</v>
-      </c>
       <c r="M97" t="n">
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q97" t="n">
         <v>0</v>
@@ -7628,24 +7146,19 @@
         <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>0</v>
-      </c>
-      <c r="T97" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Vida Reynolds</t>
+          <t>Isabella McGrath</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>683544</v>
-      </c>
-      <c r="C98" t="n">
-        <v>4</v>
-      </c>
+        <v>546310</v>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
           <t>Leinster W3</t>
@@ -7663,38 +7176,38 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Rush W2</t>
+          <t>Pembroke W3</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>27 May 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="I98" t="n">
+        <v>2</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
         <v>1</v>
       </c>
-      <c r="J98" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" t="n">
-        <v>0</v>
-      </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
@@ -7703,23 +7216,18 @@
       </c>
       <c r="S98" t="n">
         <v>0</v>
-      </c>
-      <c r="T98" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Vida Reynolds</t>
+          <t>Sinead O'Shea</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>683544</v>
-      </c>
-      <c r="C99" t="n">
-        <v>4</v>
-      </c>
+        <v>882428</v>
+      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
           <t>Leinster W3</t>
@@ -7732,21 +7240,21 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Leinster W4</t>
+          <t>Leinster W3</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Athlone W1</t>
+          <t>Rush W2</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>23 May 2026</t>
+          <t>27 May 2026</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -7777,23 +7285,18 @@
       </c>
       <c r="S99" t="n">
         <v>0</v>
-      </c>
-      <c r="T99" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Vida Reynolds</t>
+          <t>Ava Deacon</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>683544</v>
-      </c>
-      <c r="C100" t="n">
-        <v>4</v>
-      </c>
+        <v>326899</v>
+      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
           <t>Leinster W3</t>
@@ -7806,24 +7309,24 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W1</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pembroke W3</t>
+          <t>Clontarf W1</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>30 May 2026</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -7844,30 +7347,25 @@
         <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
-      </c>
-      <c r="T100" t="n">
-        <v>192</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Vida Reynolds</t>
+          <t>Ava Deacon</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>683544</v>
-      </c>
-      <c r="C101" t="n">
-        <v>4</v>
-      </c>
+        <v>326899</v>
+      </c>
+      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
           <t>Leinster W3</t>
@@ -7885,16 +7383,16 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phoenix W2</t>
+          <t>Rush W2</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>19 May 2026</t>
+          <t>27 May 2026</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -7903,16 +7401,16 @@
         <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P101" t="n">
         <v>0</v>
@@ -7924,24 +7422,19 @@
         <v>0</v>
       </c>
       <c r="S101" t="n">
-        <v>0</v>
-      </c>
-      <c r="T101" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Vida Reynolds</t>
+          <t>Ava Deacon</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>683544</v>
-      </c>
-      <c r="C102" t="n">
-        <v>4</v>
-      </c>
+        <v>326899</v>
+      </c>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
           <t>Leinster W3</t>
@@ -7954,21 +7447,21 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Leinster W4</t>
+          <t>Leinster W2</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tyrrelstown W1</t>
+          <t>Merrion W2</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>14 May 2026</t>
+          <t>26 May 2026</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -7999,68 +7492,63 @@
       </c>
       <c r="S102" t="n">
         <v>0</v>
-      </c>
-      <c r="T102" t="n">
-        <v>44</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Vida Reynolds</t>
+          <t>Ava Deacon</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>683544</v>
-      </c>
-      <c r="C103" t="n">
+        <v>326899</v>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Pembroke W3</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>20 May 2026</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>8</v>
+      </c>
+      <c r="J103" t="n">
+        <v>1</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
         <v>4</v>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Leinster W3</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>May2026</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Leinster W3</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Balbriggan W2</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>13 May 2026</t>
-        </is>
-      </c>
-      <c r="I103" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" t="n">
-        <v>0</v>
-      </c>
       <c r="M103" t="n">
         <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P103" t="n">
         <v>0</v>
@@ -8072,24 +7560,19 @@
         <v>0</v>
       </c>
       <c r="S103" t="n">
-        <v>0</v>
-      </c>
-      <c r="T103" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Vida Reynolds</t>
+          <t>Ava Deacon</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>683544</v>
-      </c>
-      <c r="C104" t="n">
-        <v>4</v>
-      </c>
+        <v>326899</v>
+      </c>
+      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
           <t>Leinster W3</t>
@@ -8107,16 +7590,16 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Clontarf W3</t>
+          <t>Phoenix W2</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>5 May 2026</t>
+          <t>19 May 2026</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8125,13 +7608,13 @@
         <v>0</v>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -8146,39 +7629,34 @@
         <v>0</v>
       </c>
       <c r="S104" t="n">
-        <v>0</v>
-      </c>
-      <c r="T104" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sriya Komati Reddy</t>
+          <t>Ava Deacon</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>3561990</v>
-      </c>
-      <c r="C105" t="n">
-        <v>4</v>
-      </c>
+        <v>326899</v>
+      </c>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
           <t>Leinster W2</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>May2026</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Leinster W2</t>
-        </is>
-      </c>
       <c r="G105" t="inlineStr">
         <is>
           <t>Pembroke W2</t>
@@ -8190,22 +7668,22 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
       </c>
       <c r="L105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
         <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -8221,26 +7699,21 @@
       </c>
       <c r="S105" t="n">
         <v>0</v>
-      </c>
-      <c r="T105" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sriya Komati Reddy</t>
+          <t>Ava Deacon</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>3561990</v>
-      </c>
-      <c r="C106" t="n">
-        <v>4</v>
-      </c>
+        <v>326899</v>
+      </c>
+      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Leinster W2</t>
+          <t>Leinster W3</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -8264,7 +7737,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="J106" t="n">
         <v>1</v>
@@ -8273,7 +7746,7 @@
         <v>0</v>
       </c>
       <c r="L106" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M106" t="n">
         <v>0</v>
@@ -8282,10 +7755,10 @@
         <v>16</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -8295,71 +7768,66 @@
       </c>
       <c r="S106" t="n">
         <v>0</v>
-      </c>
-      <c r="T106" t="n">
-        <v>140</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sriya Komati Reddy</t>
+          <t>Daphne Deacon</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>3561990</v>
-      </c>
-      <c r="C107" t="n">
+        <v>691434</v>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Leinster W4</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Leinster W4</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Athlone W1</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>23 May 2026</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>30</v>
+      </c>
+      <c r="J107" t="n">
         <v>4</v>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Leinster W2</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>May2026</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Leinster W1</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Malahide W1</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>26 Apr 2026</t>
-        </is>
-      </c>
-      <c r="I107" t="n">
-        <v>7</v>
-      </c>
-      <c r="J107" t="n">
-        <v>0</v>
-      </c>
       <c r="K107" t="n">
         <v>0</v>
       </c>
       <c r="L107" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M107" t="n">
         <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
@@ -8370,25 +7838,20 @@
       <c r="S107" t="n">
         <v>1</v>
       </c>
-      <c r="T107" t="n">
-        <v>28</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Rachel Sparrow</t>
+          <t>Daphne Deacon</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>683019</v>
-      </c>
-      <c r="C108" t="n">
-        <v>4</v>
-      </c>
+        <v>691434</v>
+      </c>
+      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Leinster W3</t>
+          <t>Leinster W4</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -8403,16 +7866,16 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Athlone W1</t>
+          <t>Tyrrelstown W1</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>23 May 2026</t>
+          <t>14 May 2026</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8421,16 +7884,16 @@
         <v>0</v>
       </c>
       <c r="L108" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M108" t="n">
         <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="O108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P108" t="n">
         <v>0</v>
@@ -8442,24 +7905,19 @@
         <v>0</v>
       </c>
       <c r="S108" t="n">
-        <v>1</v>
-      </c>
-      <c r="T108" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Rachel Sparrow</t>
+          <t>Margaret O'Donoghue</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>683019</v>
-      </c>
-      <c r="C109" t="n">
-        <v>4</v>
-      </c>
+        <v>554268</v>
+      </c>
+      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
           <t>Leinster W3</t>
@@ -8477,16 +7935,16 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tyrrelstown W1</t>
+          <t>Athlone W1</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>14 May 2026</t>
+          <t>23 May 2026</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8495,13 +7953,13 @@
         <v>0</v>
       </c>
       <c r="L109" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M109" t="n">
         <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="O109" t="n">
         <v>1</v>
@@ -8518,22 +7976,17 @@
       <c r="S109" t="n">
         <v>0</v>
       </c>
-      <c r="T109" t="n">
-        <v>48</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Lorraine Bagnall</t>
+          <t>Margaret O'Donoghue</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>687333</v>
-      </c>
-      <c r="C110" t="n">
-        <v>4</v>
-      </c>
+        <v>554268</v>
+      </c>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
           <t>Leinster W3</t>
@@ -8560,7 +8013,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8569,13 +8022,13 @@
         <v>0</v>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M110" t="n">
         <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -8591,26 +8044,21 @@
       </c>
       <c r="S110" t="n">
         <v>0</v>
-      </c>
-      <c r="T110" t="n">
-        <v>92</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Lavanya Rajesh</t>
+          <t>Margaret O'Donoghue</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>3279566</v>
-      </c>
-      <c r="C111" t="n">
-        <v>4</v>
-      </c>
+        <v>554268</v>
+      </c>
+      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Leinster W4</t>
+          <t>Leinster W3</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -8620,21 +8068,21 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Leinster W4</t>
+          <t>Leinster W3</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Athlone W1</t>
+          <t>Clontarf W3</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>23 May 2026</t>
+          <t>5 May 2026</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -8665,46 +8113,41 @@
       </c>
       <c r="S111" t="n">
         <v>0</v>
-      </c>
-      <c r="T111" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Lavanya Rajesh</t>
+          <t>Alison Crawford</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>3279566</v>
-      </c>
-      <c r="C112" t="n">
-        <v>4</v>
-      </c>
+        <v>76412</v>
+      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
           <t>Leinster W4</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>May2026</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Leinster W3</t>
-        </is>
-      </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Pembroke W3</t>
+          <t>Tyrrelstown W1</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>14 May 2026</t>
         </is>
       </c>
       <c r="I112" t="n">
@@ -8738,84 +8181,1594 @@
         <v>0</v>
       </c>
       <c r="S112" t="n">
-        <v>0</v>
-      </c>
-      <c r="T112" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
+          <t>Sadhbh Smyth</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>3281758</v>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Rush W2</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>27 May 2026</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>3</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" t="n">
+        <v>23</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Sadhbh Smyth</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>3281758</v>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Leinster W4</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Athlone W1</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>23 May 2026</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>14</v>
+      </c>
+      <c r="J114" t="n">
+        <v>1</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
+        <v>5</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="n">
+        <v>34</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>0</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Sadhbh Smyth</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>3281758</v>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Pembroke W3</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>20 May 2026</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>2</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="n">
+        <v>10</v>
+      </c>
+      <c r="O115" t="n">
+        <v>2</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Sadhbh Smyth</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>3281758</v>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Phoenix W2</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>19 May 2026</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Sadhbh Smyth</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>3281758</v>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Leinster W4</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Tyrrelstown W1</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>14 May 2026</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>12</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="n">
+        <v>4</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" t="n">
+        <v>27</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Sadhbh Smyth</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>3281758</v>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Balbriggan W2</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>13 May 2026</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Sadhbh Smyth</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>3281758</v>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Clontarf W3</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>5 May 2026</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Vida Reynolds</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>683544</v>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Rush W2</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>27 May 2026</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>1</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Vida Reynolds</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>683544</v>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Leinster W4</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Athlone W1</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>23 May 2026</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Vida Reynolds</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>683544</v>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Pembroke W3</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>20 May 2026</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>38</v>
+      </c>
+      <c r="J122" t="n">
+        <v>5</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>1</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Vida Reynolds</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>683544</v>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Phoenix W2</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>19 May 2026</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Vida Reynolds</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>683544</v>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Leinster W4</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Tyrrelstown W1</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>14 May 2026</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>11</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Vida Reynolds</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>683544</v>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Balbriggan W2</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>13 May 2026</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Vida Reynolds</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>683544</v>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Clontarf W3</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>5 May 2026</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Sriya Komati Reddy</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>3561990</v>
+      </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Leinster W2</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Leinster W2</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Pembroke W2</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>12 May 2026</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>4</v>
+      </c>
+      <c r="J127" t="n">
+        <v>1</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>2</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="n">
+        <v>18</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Sriya Komati Reddy</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>3561990</v>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Leinster W2</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Clontarf W3</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>5 May 2026</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>31</v>
+      </c>
+      <c r="J128" t="n">
+        <v>1</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>4</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="n">
+        <v>16</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Sriya Komati Reddy</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>3561990</v>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Leinster W2</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Leinster W1</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Malahide W1</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>26 Apr 2026</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>7</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
+        <v>4</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="n">
+        <v>24</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Rachel Sparrow</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>683019</v>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Leinster W4</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Athlone W1</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>23 May 2026</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
+        <v>5</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" t="n">
+        <v>26</v>
+      </c>
+      <c r="O130" t="n">
+        <v>2</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Rachel Sparrow</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>683019</v>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Leinster W4</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Tyrrelstown W1</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>14 May 2026</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>8</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>4</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="n">
+        <v>26</v>
+      </c>
+      <c r="O131" t="n">
+        <v>1</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Lorraine Bagnall</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>687333</v>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Leinster W4</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Tyrrelstown W1</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>14 May 2026</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>23</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
           <t>Lavanya Rajesh</t>
         </is>
       </c>
-      <c r="B113" t="n">
+      <c r="B133" t="n">
         <v>3279566</v>
       </c>
-      <c r="C113" t="n">
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Leinster W4</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Leinster W4</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Athlone W1</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>23 May 2026</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
         <v>4</v>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Lavanya Rajesh</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>3279566</v>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
         <is>
           <t>Leinster W4</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>May2026</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Leinster W3</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Pembroke W3</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>20 May 2026</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Lavanya Rajesh</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>3279566</v>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
         <is>
           <t>Leinster W4</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>May2026</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Leinster W4</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
         <is>
           <t>Tyrrelstown W1</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="H135" t="inlineStr">
         <is>
           <t>14 May 2026</t>
         </is>
       </c>
-      <c r="I113" t="n">
+      <c r="I135" t="n">
         <v>2</v>
       </c>
-      <c r="J113" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" t="n">
-        <v>0</v>
-      </c>
-      <c r="L113" t="n">
-        <v>0</v>
-      </c>
-      <c r="M113" t="n">
-        <v>0</v>
-      </c>
-      <c r="N113" t="n">
-        <v>0</v>
-      </c>
-      <c r="O113" t="n">
-        <v>0</v>
-      </c>
-      <c r="P113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
-      <c r="R113" t="n">
-        <v>0</v>
-      </c>
-      <c r="S113" t="n">
-        <v>0</v>
-      </c>
-      <c r="T113" t="n">
-        <v>8</v>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
